--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488242_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488242_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.9932</v>
+        <v>10.8953</v>
       </c>
       <c r="E2" t="n">
-        <v>9.1418</v>
+        <v>9.043799999999999</v>
       </c>
       <c r="F2" t="n">
         <v>1.8515</v>
@@ -610,10 +610,10 @@
         <v>1.297</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5894</v>
+        <v>0.4915</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1604</v>
+        <v>0.0625</v>
       </c>
       <c r="U2" t="n">
         <v>0.429</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.9741</v>
+        <v>6.654</v>
       </c>
       <c r="E3" t="n">
         <v>4.0937</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8804</v>
+        <v>2.5603</v>
       </c>
       <c r="G3" t="n">
         <v>4.4394</v>
@@ -688,13 +688,13 @@
         <v>2.9646</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1085</v>
+        <v>0.7884</v>
       </c>
       <c r="T3" t="n">
         <v>0.3209</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7876</v>
+        <v>0.4675</v>
       </c>
       <c r="V3" t="n">
         <v>0.3144</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.904</v>
+        <v>3.3947</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9359</v>
+        <v>1.2297</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9681</v>
+        <v>2.165</v>
       </c>
       <c r="G4" t="n">
         <v>1.8251</v>
@@ -766,13 +766,13 @@
         <v>1.8529</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.774</v>
+        <v>-0.2832</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6566</v>
+        <v>-0.3628</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1174</v>
+        <v>0.0796</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3915</v>
+        <v>2.7838</v>
       </c>
       <c r="E5" t="n">
-        <v>1.125</v>
+        <v>1.4188</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2666</v>
+        <v>1.365</v>
       </c>
       <c r="G5" t="n">
         <v>1.5705</v>
@@ -844,13 +844,13 @@
         <v>1.297</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5113</v>
+        <v>-0.1191</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6019</v>
+        <v>-0.3081</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0905</v>
+        <v>0.189</v>
       </c>
       <c r="V5" t="n">
         <v>1.8883</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0212</v>
+        <v>0.6156</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0554</v>
+        <v>-0.4678</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0342</v>
+        <v>1.0834</v>
       </c>
       <c r="G8" t="n">
         <v>1.2444</v>
@@ -1078,13 +1078,13 @@
         <v>2.9646</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8389</v>
+        <v>-0.2021</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0396</v>
+        <v>-0.452</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2007</v>
+        <v>0.2499</v>
       </c>
       <c r="V8" t="n">
         <v>0.3144</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ CAPELLIN</t>
+          <t>J. NIELSEN HIDALGO MARTIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.113</v>
+        <v>-0.8081</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4699</v>
+        <v>-0.0195</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3568</v>
+        <v>-0.7886</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8676</v>
+        <v>-0.5744</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3076</v>
+        <v>1.1107</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1751</v>
+        <v>-1.6851</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3057</v>
+        <v>0.4606</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1.0092</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3057</v>
+        <v>-0.5486</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4381</v>
+        <v>-1.035</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3076</v>
+        <v>0.1016</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1306</v>
+        <v>-1.1366</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2455</v>
+        <v>0.1548</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1641</v>
+        <v>0.1499</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0813</v>
+        <v>0.005</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.9444</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2375</v>
+        <v>-0.9671999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0527</v>
+        <v>0.1506</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2902</v>
+        <v>-1.1178</v>
       </c>
       <c r="G10" t="n">
         <v>-2.3629</v>
@@ -1234,13 +1234,13 @@
         <v>1.4823</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3564</v>
+        <v>-0.0861</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2226</v>
+        <v>-0.1246</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1338</v>
+        <v>0.0385</v>
       </c>
       <c r="V10" t="n">
         <v>-0.0005</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. NIELSEN HIDALGO MARTIN</t>
+          <t>J. RODRIGUEZ CAPELLIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4696</v>
+        <v>-1.0392</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6071</v>
+        <v>-1.4699</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8625</v>
+        <v>0.4307</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5744</v>
+        <v>-0.8676</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1107</v>
+        <v>0.3076</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.6851</v>
+        <v>-1.1751</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4606</v>
+        <v>-1.3057</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0092</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5486</v>
+        <v>-1.3057</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.035</v>
+        <v>0.4381</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1016</v>
+        <v>0.3076</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.1366</v>
+        <v>0.1306</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5066000000000001</v>
+        <v>-0.1716</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4377</v>
+        <v>-0.1641</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0689</v>
+        <v>-0.0075</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9444</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.7158</v>
+        <v>-2.9866</v>
       </c>
       <c r="E12" t="n">
         <v>-2.4451</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2707</v>
+        <v>-0.5415</v>
       </c>
       <c r="G12" t="n">
         <v>-1.3624</v>
@@ -1390,13 +1390,13 @@
         <v>0.7411</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3877</v>
+        <v>0.1169</v>
       </c>
       <c r="T12" t="n">
         <v>-0.0037</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3914</v>
+        <v>0.1206</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6294</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LEIRO</t>
+          <t>R. ALOGO EVUNA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.4591</v>
+        <v>-3.9891</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.8446</v>
+        <v>-0.6055</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3854</v>
+        <v>-3.3836</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.422</v>
+        <v>-2.0018</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.6833</v>
+        <v>-0.1648</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7387</v>
+        <v>-1.8371</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.8968</v>
+        <v>-0.1834</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.1871</v>
+        <v>0.3865</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2903</v>
+        <v>-0.5699</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.5251</v>
+        <v>-1.8184</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4961</v>
+        <v>-0.5513</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.029</v>
+        <v>-1.2671</v>
       </c>
       <c r="P13" t="n">
+        <v>-1.1117</v>
+      </c>
+      <c r="Q13" t="n">
         <v>-1.8529</v>
       </c>
-      <c r="Q13" t="n">
-        <v>-3.7057</v>
-      </c>
       <c r="R13" t="n">
-        <v>1.8529</v>
+        <v>0.7411</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5013</v>
+        <v>0.3833</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4436</v>
+        <v>0.1719</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0577</v>
+        <v>0.2114</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3144</v>
+        <v>-1.2589</v>
       </c>
       <c r="W13" t="n">
-        <v>0.3144</v>
+        <v>1.2589</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-2.5177</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. ALOGO EVUNA</t>
+          <t>A. RODRIGUEZ LEIRO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.7681</v>
+        <v>-5.0747</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-5.5094</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.2605</v>
+        <v>0.4347</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.0018</v>
+        <v>-4.422</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1648</v>
+        <v>-3.6833</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.8371</v>
+        <v>-0.7387</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1834</v>
+        <v>-2.8968</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3865</v>
+        <v>-3.1871</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5699</v>
+        <v>0.2903</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.8184</v>
+        <v>-1.5251</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5513</v>
+        <v>-0.4961</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.2671</v>
+        <v>-1.029</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.1117</v>
+        <v>-1.8529</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.8529</v>
+        <v>-3.7057</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7411</v>
+        <v>1.8529</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6044</v>
+        <v>0.8857</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2699</v>
+        <v>0.7788</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3345</v>
+        <v>0.1069</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2589</v>
+        <v>0.3144</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2589</v>
+        <v>0.3144</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.5177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1591,10 +1591,10 @@
         <v>8.758599999999998</v>
       </c>
       <c r="H15" t="n">
-        <v>3.075599999999999</v>
+        <v>3.0756</v>
       </c>
       <c r="I15" t="n">
-        <v>5.682800000000002</v>
+        <v>5.6828</v>
       </c>
       <c r="J15" t="n">
         <v>16.9891</v>
@@ -1606,7 +1606,7 @@
         <v>12.5933</v>
       </c>
       <c r="M15" t="n">
-        <v>-8.230500000000001</v>
+        <v>-8.230499999999999</v>
       </c>
       <c r="N15" t="n">
         <v>-1.3198</v>
@@ -1615,7 +1615,7 @@
         <v>-6.9106</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0001000000000006551</v>
+        <v>9.999999999976694e-05</v>
       </c>
       <c r="Q15" t="n">
         <v>-15.7494</v>
@@ -1624,13 +1624,13 @@
         <v>15.7494</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9586</v>
+        <v>1.9585</v>
       </c>
       <c r="T15" t="n">
-        <v>0.06860000000000016</v>
+        <v>0.06869999999999987</v>
       </c>
       <c r="U15" t="n">
-        <v>1.89</v>
+        <v>1.8899</v>
       </c>
       <c r="V15" t="n">
         <v>1.5716</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.2449</v>
+        <v>3.166</v>
       </c>
       <c r="E16" t="n">
-        <v>4.4584</v>
+        <v>3.675</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2135</v>
+        <v>-0.5089</v>
       </c>
       <c r="G16" t="n">
         <v>2.617</v>
@@ -1702,13 +1702,13 @@
         <v>2.7793</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0366</v>
+        <v>-0.0423</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7549</v>
+        <v>-0.0286</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2818</v>
+        <v>-0.0137</v>
       </c>
       <c r="V16" t="n">
         <v>1.8883</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. CARO SERRANO</t>
+          <t>F. VALDIVIA SANTILLANA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0738</v>
+        <v>0.1222</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8097</v>
+        <v>-0.4277</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8835</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.3209</v>
+        <v>-0.0728</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0644</v>
+        <v>-0.6337</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.2565</v>
+        <v>0.5609</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3757</v>
+        <v>0.6919</v>
       </c>
       <c r="K17" t="n">
-        <v>0.365</v>
+        <v>-0.1375</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0107</v>
+        <v>0.8294</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6966</v>
+        <v>-0.7647</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4294</v>
+        <v>-0.4961</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2671</v>
+        <v>-0.2686</v>
       </c>
       <c r="P17" t="n">
         <v>0.5558999999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.297</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.8529</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6912</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>0.434</v>
+        <v>-0.452</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2572</v>
+        <v>-0.2239</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. VALDIVIA SANTILLANA</t>
+          <t>J. CARO SERRANO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9578</v>
+        <v>-0.4902</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0153</v>
+        <v>0.418</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0575</v>
+        <v>-0.9082</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0728</v>
+        <v>-1.3209</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6337</v>
+        <v>-0.0644</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5609</v>
+        <v>-1.2565</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6919</v>
+        <v>0.3757</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1375</v>
+        <v>0.365</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8294</v>
+        <v>0.0107</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7647</v>
+        <v>-1.6966</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4961</v>
+        <v>-0.4294</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2686</v>
+        <v>-1.2671</v>
       </c>
       <c r="P18" t="n">
         <v>0.5558999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.297</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8529</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.7559</v>
+        <v>0.2748</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0396</v>
+        <v>0.0423</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7163</v>
+        <v>0.2325</v>
       </c>
       <c r="V18" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0673</v>
+        <v>-0.797</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9762999999999999</v>
+        <v>-0.8783</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0911</v>
+        <v>0.0813</v>
       </c>
       <c r="G19" t="n">
         <v>-1.6301</v>
@@ -1936,13 +1936,13 @@
         <v>2.2234</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2345</v>
+        <v>0.0358</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1131</v>
+        <v>-0.0152</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1214</v>
+        <v>0.051</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3144</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. QUINTA RAMOS</t>
+          <t>M. MALICK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3365</v>
+        <v>-1.8254</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3588</v>
+        <v>1.4193</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9777</v>
+        <v>-3.2447</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3768</v>
+        <v>0.868</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0556</v>
+        <v>-3.5649</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6787</v>
+        <v>4.4329</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5737</v>
+        <v>5.0115</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7857</v>
+        <v>-2.7235</v>
       </c>
       <c r="L20" t="n">
-        <v>0.788</v>
+        <v>7.735</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1968</v>
+        <v>-4.1435</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2699</v>
+        <v>-0.8414</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4667</v>
+        <v>-3.3021</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9264</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0382</v>
+        <v>-2.9646</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1117</v>
+        <v>2.594</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4158</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1057</v>
+        <v>-0.6277</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3101</v>
+        <v>-0.1219</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.2027</v>
+        <v>-1.5733</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.2027</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. MALICK</t>
+          <t>J. QUINTA RAMOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4863</v>
+        <v>-2.6314</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7338</v>
+        <v>-0.4567</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.2201</v>
+        <v>-2.1747</v>
       </c>
       <c r="G21" t="n">
-        <v>0.868</v>
+        <v>0.3768</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.5649</v>
+        <v>1.0556</v>
       </c>
       <c r="I21" t="n">
-        <v>4.4329</v>
+        <v>-0.6787</v>
       </c>
       <c r="J21" t="n">
-        <v>5.0115</v>
+        <v>1.5737</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.7235</v>
+        <v>0.7857</v>
       </c>
       <c r="L21" t="n">
-        <v>7.735</v>
+        <v>0.788</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.1435</v>
+        <v>-1.1968</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8414</v>
+        <v>0.2699</v>
       </c>
       <c r="O21" t="n">
-        <v>-3.3021</v>
+        <v>-1.4667</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3706</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9646</v>
+        <v>-2.0382</v>
       </c>
       <c r="R21" t="n">
-        <v>2.594</v>
+        <v>1.1117</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4104</v>
+        <v>0.1209</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3132</v>
+        <v>0.0078</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0973</v>
+        <v>0.1131</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.5733</v>
+        <v>-2.2027</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.5733</v>
+        <v>-2.2027</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.7462</v>
+        <v>-4.402</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0303</v>
+        <v>-3.9324</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7158</v>
+        <v>-0.4696</v>
       </c>
       <c r="G22" t="n">
         <v>-4.5264</v>
@@ -2170,13 +2170,13 @@
         <v>1.6676</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0906</v>
+        <v>-0.7464</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6019</v>
+        <v>-0.5039</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4887</v>
+        <v>-0.2425</v>
       </c>
       <c r="V22" t="n">
         <v>0.315</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.8658</v>
+        <v>-5.431</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6804</v>
+        <v>-3.8762</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1854</v>
+        <v>-1.5548</v>
       </c>
       <c r="G23" t="n">
         <v>-5.0703</v>
@@ -2248,13 +2248,13 @@
         <v>2.9646</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3892</v>
+        <v>-0.176</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1169</v>
+        <v>-0.3127</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5061</v>
+        <v>0.1368</v>
       </c>
       <c r="V23" t="n">
         <v>0.0005</v>
@@ -2284,10 +2284,10 @@
         <v>-12.2888</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.059200000000001</v>
+        <v>-4.059000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.2296</v>
+        <v>-8.229699999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-8.758699999999999</v>
@@ -2329,10 +2329,10 @@
         <v>-1.9586</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.8901</v>
+        <v>-1.89</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.06850000000000012</v>
+        <v>-0.06859999999999992</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5716</v>
